--- a/catalogues/SETTLEMENTS-CATALOGUES.xlsx
+++ b/catalogues/SETTLEMENTS-CATALOGUES.xlsx
@@ -42,7 +42,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ranks'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Skills'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Skills'!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Progression'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Weapon Classes'!$A$1:$L$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Weapon Characteristics'!$A$1:$G$1</definedName>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -737,7 +737,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>The Ruled column</t>
+          <t>The Requires column (Skills)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr"/>
@@ -745,487 +745,535 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>(blank) or Ross</t>
+          <t>Name the skill it needs</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>You decided it. This is the default — leave it blank and it means yours.</t>
+          <t>A skill that uses a state only another skill can create must name it. Squeeze needs Grapple; without it the card is dead.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Climbing a chain costs slots</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Worked out from another rule rather than decided. Fine to keep, but it is an inference, not a ruling.</t>
+          <t>To take a T3 in a chain you need its T2, which needs its T1 — so a Leader spending all three slots on one chain is the whole build. That is the intended cost.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>carried-over</t>
+          <t>Leave blank if standalone</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Brought in from the old system without being re-checked.</t>
+          <t>Most skills need nothing. Only the chained ones fill this in.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>unruled</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Placeholder. Nobody has actually decided this yet.</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Why it exists</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>"Only a Leader ever reaches T3" was a derived gloss that entered with the master doc on 2026-08-05, restating a July cap table — then got quoted back at you as a design constraint you never set. This column makes that impossible to repeat.</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>The Ruled column</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>(blank) or Ross</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>You decided it. This is the default — leave it blank and it means yours.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Sheets that are new</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr"/>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Worked out from another rule rather than decided. Fine to keep, but it is an inference, not a ruling.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Chems, Drones</t>
+          <t>carried-over</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>No catalogue exists in the rules today. Both are named in the setting and referenced by built structures.</t>
+          <t>Brought in from the old system without being re-checked.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Weapon Drawbacks</t>
+          <t>unruled</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Split out from Characteristics — a refund is a price, and they were never tiered.</t>
+          <t>Placeholder. Nobody has actually decided this yet.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Scenario Twists, Glorious Deeds,</t>
+          <t>Why it exists</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Existed in the rules but never as their own catalogue.</t>
+          <t>"Only a Leader ever reaches T3" was a derived gloss that entered with the master doc on 2026-08-05, restating a July cap table — then got quoted back at you as a design constraint you never set. This column makes that impossible to repeat.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Fate Table, Injuries &amp; Scars</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sheets that are new</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr"/>
+    </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Progress</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Chems, Drones</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>No catalogue exists in the rules today. Both are named in the setting and referenced by built structures.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Weapon Drawbacks</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Split out from Characteristics — a refund is a price, and they were never tiered.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Scenario Twists, Glorious Deeds,</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Existed in the rules but never as their own catalogue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Fate Table, Injuries &amp; Scars</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>Ranks</t>
         </is>
       </c>
-      <c r="B32" s="5">
+      <c r="B37" s="5">
         <f>COUNTA('Ranks'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Skills</t>
         </is>
       </c>
-      <c r="B33" s="5">
+      <c r="B38" s="5">
         <f>COUNTA('Skills'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Progression</t>
         </is>
       </c>
-      <c r="B34" s="5">
+      <c r="B39" s="5">
         <f>COUNTA('Progression'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Weapon Classes</t>
         </is>
       </c>
-      <c r="B35" s="5">
+      <c r="B40" s="5">
         <f>COUNTA('Weapon Classes'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Weapon Characteristics</t>
         </is>
       </c>
-      <c r="B36" s="5">
+      <c r="B41" s="5">
         <f>COUNTA('Weapon Characteristics'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Weapon Drawbacks</t>
         </is>
       </c>
-      <c r="B37" s="5">
+      <c r="B42" s="5">
         <f>COUNTA('Weapon Drawbacks'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Armour</t>
         </is>
       </c>
-      <c r="B38" s="5">
+      <c r="B43" s="5">
         <f>COUNTA('Armour'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="B39" s="5">
+      <c r="B44" s="5">
         <f>COUNTA('Equipment'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Chems</t>
         </is>
       </c>
-      <c r="B40" s="5">
+      <c r="B45" s="5">
         <f>COUNTA('Chems'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Drones</t>
         </is>
       </c>
-      <c r="B41" s="5">
+      <c r="B46" s="5">
         <f>COUNTA('Drones'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Turrets</t>
         </is>
       </c>
-      <c r="B42" s="5">
+      <c r="B47" s="5">
         <f>COUNTA('Turrets'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Mine Chassis</t>
         </is>
       </c>
-      <c r="B43" s="5">
+      <c r="B48" s="5">
         <f>COUNTA('Mine Chassis'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Mine Payloads</t>
         </is>
       </c>
-      <c r="B44" s="5">
+      <c r="B49" s="5">
         <f>COUNTA('Mine Payloads'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Traps</t>
         </is>
       </c>
-      <c r="B45" s="5">
+      <c r="B50" s="5">
         <f>COUNTA('Traps'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Beacons</t>
         </is>
       </c>
-      <c r="B46" s="5">
+      <c r="B51" s="5">
         <f>COUNTA('Beacons'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Conditions</t>
         </is>
       </c>
-      <c r="B47" s="5">
+      <c r="B52" s="5">
         <f>COUNTA('Conditions'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Reactions</t>
         </is>
       </c>
-      <c r="B48" s="5">
+      <c r="B53" s="5">
         <f>COUNTA('Reactions'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Terrain Types</t>
         </is>
       </c>
-      <c r="B49" s="5">
+      <c r="B54" s="5">
         <f>COUNTA('Terrain Types'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Terrain Hazards</t>
         </is>
       </c>
-      <c r="B50" s="5">
+      <c r="B55" s="5">
         <f>COUNTA('Terrain Hazards'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Terrain Verbs</t>
         </is>
       </c>
-      <c r="B51" s="5">
+      <c r="B56" s="5">
         <f>COUNTA('Terrain Verbs'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="B52" s="5">
+      <c r="B57" s="5">
         <f>COUNTA('Infrastructure'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
-      <c r="B53" s="5">
+      <c r="B58" s="5">
         <f>COUNTA('Structures'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Worker Benefits</t>
         </is>
       </c>
-      <c r="B54" s="5">
+      <c r="B59" s="5">
         <f>COUNTA('Worker Benefits'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Scenarios</t>
         </is>
       </c>
-      <c r="B55" s="5">
+      <c r="B60" s="5">
         <f>COUNTA('Scenarios'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Scenario Twists</t>
         </is>
       </c>
-      <c r="B56" s="5">
+      <c r="B61" s="5">
         <f>COUNTA('Scenario Twists'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Factions</t>
         </is>
       </c>
-      <c r="B57" s="5">
+      <c r="B62" s="5">
         <f>COUNTA('Factions'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Loot Table</t>
         </is>
       </c>
-      <c r="B58" s="5">
+      <c r="B63" s="5">
         <f>COUNTA('Loot Table'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
       </c>
-      <c r="B59" s="5">
+      <c r="B64" s="5">
         <f>COUNTA('Events'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Glorious Deeds</t>
         </is>
       </c>
-      <c r="B60" s="5">
+      <c r="B65" s="5">
         <f>COUNTA('Glorious Deeds'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Fate Table</t>
         </is>
       </c>
-      <c r="B61" s="5">
+      <c r="B66" s="5">
         <f>COUNTA('Fate Table'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>Injuries &amp; Scars</t>
         </is>
       </c>
-      <c r="B62" s="5">
+      <c r="B67" s="5">
         <f>COUNTA('Injuries &amp; Scars'!A2:A400)</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B63" s="3">
-        <f>SUM(B32:B62)</f>
+      <c r="B68" s="3">
+        <f>SUM(B37:B67)</f>
         <v/>
       </c>
     </row>
@@ -3152,16 +3200,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3182,20 +3231,25 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
+          <t>Requires</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
           <t>Effect</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Ruled</t>
         </is>
@@ -3204,40 +3258,49 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Bank Shot</t>
+          <t>Squeeze</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>DEX</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>When Heavy Cover causes your ranged attack to miss by exactly 1, a target touching that cover becomes Pinned; make no Injury roll.</t>
+          <t>Grapple</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Suppressor</t>
-        </is>
-      </c>
-      <c r="F2" s="8" t="inlineStr"/>
+          <t>As an Action, make an opposed STR test against an enemy you have Grappled. On a win, it suffers an automatic unarmed hit; make only the Injury roll.</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>Grappler</t>
+        </is>
+      </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
+          <t>Cannot be used without Grapple</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
           <t>Ross</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:H1"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Who ruled this?" prompt="Blank or Ross = your decision. derived = worked out from another rule. carried-over = brought in from the old system, unchecked. unruled = placeholder, nobody has decided." type="list">
+    <dataValidation sqref="H2:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Who ruled this?" prompt="Blank or Ross = your decision. derived = worked out from another rule. carried-over = brought in from the old system, unchecked. unruled = placeholder, nobody has decided." type="list">
       <formula1>"Ross,derived,carried-over,unruled"</formula1>
     </dataValidation>
   </dataValidations>
